--- a/rtss-pre1917/charts/birth-death-counts/adjusted-stage2-final/Елисаветпольская.xlsx
+++ b/rtss-pre1917/charts/birth-death-counts/adjusted-stage2-final/Елисаветпольская.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t xml:space="preserve">Числа рождений и смертей для </t>
   </si>
@@ -1956,10 +1956,10 @@
         <v>1881.0</v>
       </c>
       <c r="B7" s="7" t="n">
-        <v>18742.0</v>
+        <v>18860.0</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>12075.0</v>
+        <v>12955.0</v>
       </c>
       <c r="D7" s="7"/>
       <c r="E7" s="7"/>
@@ -1975,10 +1975,10 @@
         <v>1882.0</v>
       </c>
       <c r="B8" s="7" t="n">
-        <v>18904.0</v>
+        <v>19004.0</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>12180.0</v>
+        <v>13055.0</v>
       </c>
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
@@ -1994,10 +1994,10 @@
         <v>1883.0</v>
       </c>
       <c r="B9" s="7" t="n">
-        <v>19067.0</v>
+        <v>19150.0</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>12285.0</v>
+        <v>13155.0</v>
       </c>
       <c r="D9" s="7"/>
       <c r="E9" s="7"/>
@@ -2013,10 +2013,10 @@
         <v>1884.0</v>
       </c>
       <c r="B10" s="7" t="n">
-        <v>19231.0</v>
+        <v>19296.0</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>12390.0</v>
+        <v>13256.0</v>
       </c>
       <c r="D10" s="7"/>
       <c r="E10" s="7"/>
@@ -2032,10 +2032,10 @@
         <v>1885.0</v>
       </c>
       <c r="B11" s="7" t="n">
-        <v>19397.0</v>
+        <v>19444.0</v>
       </c>
       <c r="C11" s="7" t="n">
-        <v>12497.0</v>
+        <v>13358.0</v>
       </c>
       <c r="D11" s="7"/>
       <c r="E11" s="7"/>
@@ -2051,10 +2051,10 @@
         <v>1886.0</v>
       </c>
       <c r="B12" s="7" t="n">
-        <v>8206.0</v>
+        <v>19593.0</v>
       </c>
       <c r="C12" s="7" t="n">
-        <v>7950.0</v>
+        <v>13460.0</v>
       </c>
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
